--- a/data/input/sample_run_01.xlsx
+++ b/data/input/sample_run_01.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This technical report evaluates the dynamic stability and power grid integration parameters for the primary utility inverter bank. Measurements were acquired via Matlab Simulink and PyTap run routines under step-load conditions.</t>
+          <t>This technical report evaluates the dynamic stability and power grid integration parameters for the primary utility inverter bank. Measurements were acquired via ETAP simulation and related transient run routines under step-load conditions.</t>
         </is>
       </c>
     </row>
